--- a/data/trans_dic/P1414-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1414-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,46</t>
+          <t>0,25; 2,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,08</t>
+          <t>2,87; 5,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,63</t>
+          <t>3,86; 6,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,1</t>
+          <t>6,17; 9,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,1</t>
+          <t>1,8; 3,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,89</t>
+          <t>2,2; 3,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,84</t>
+          <t>3,99; 5,93</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -788,32 +788,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,53</t>
+          <t>0,06; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,89</t>
+          <t>0,29; 0,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,62</t>
+          <t>0,16; 0,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,83</t>
+          <t>1,42; 2,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,22</t>
+          <t>2,48; 4,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,83</t>
+          <t>2,97; 4,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,35</t>
+          <t>1,49; 2,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,04</t>
+          <t>1,62; 2,3</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,06</t>
+          <t>0,08; 0,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,27</t>
+          <t>0,43; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,95</t>
+          <t>0,75; 3,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,2</t>
+          <t>1,24; 3,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,42</t>
+          <t>0,19; 1,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,9</t>
+          <t>0,49; 1,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,78</t>
+          <t>0,74; 1,81</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,43</t>
+          <t>0,09; 0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,7</t>
+          <t>0,22; 0,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,72</t>
+          <t>0,26; 0,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,22</t>
+          <t>2,11; 3,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,17</t>
+          <t>2,96; 4,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,46</t>
+          <t>3,67; 4,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,75</t>
+          <t>1,18; 1,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,39</t>
+          <t>1,69; 2,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,5</t>
+          <t>2,08; 2,63</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>62314</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60524</t>
+          <t>67291</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1006; 8541</t>
+          <t>1010; 9094</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4927</t>
+          <t>0; 4979</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1534; 12549</t>
+          <t>1436; 12678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38040; 67879</t>
+          <t>38328; 66986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36981; 65971</t>
+          <t>38431; 65985</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45312; 68140</t>
+          <t>50384; 74576</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41379; 71633</t>
+          <t>41657; 71955</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38733; 68012</t>
+          <t>38396; 68237</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50465; 73604</t>
+          <t>55554; 82424</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>77589</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77106</t>
+          <t>85004</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1078; 10395</t>
+          <t>1140; 10347</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5268; 18491</t>
+          <t>6061; 19799</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3110; 14074</t>
+          <t>3464; 14024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24313; 49599</t>
+          <t>24944; 49742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51354; 83869</t>
+          <t>49372; 82857</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49923; 85380</t>
+          <t>64198; 91108</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29458; 54487</t>
+          <t>29233; 54561</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60143; 95499</t>
+          <t>60523; 95475</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58461; 92274</t>
+          <t>70986; 100993</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>16745</t>
         </is>
       </c>
     </row>
@@ -1637,42 +1637,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8645</t>
+          <t>0; 8400</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>574; 6852</t>
+          <t>578; 6912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1652; 14983</t>
+          <t>1965; 15421</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4152; 16224</t>
+          <t>4146; 16522</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8754; 21102</t>
+          <t>9066; 22990</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1008; 13380</t>
+          <t>1811; 15027</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5664; 20786</t>
+          <t>5402; 19728</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10108; 23204</t>
+          <t>10734; 26175</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>139021</t>
+          <t>154273</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>153325</t>
+          <t>169040</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3199; 14768</t>
+          <t>3149; 14302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7833; 23622</t>
+          <t>7330; 22936</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7975; 24661</t>
+          <t>8982; 25651</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74460; 114168</t>
+          <t>74810; 113815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>104248; 147360</t>
+          <t>104497; 148655</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114264; 162308</t>
+          <t>136027; 172249</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82405; 121781</t>
+          <t>82529; 120909</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117917; 165465</t>
+          <t>116482; 165345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129263; 176942</t>
+          <t>150529; 190245</t>
         </is>
       </c>
     </row>
